--- a/www/download/IND.gdp.s.du.rpO1.xlsx
+++ b/www/download/IND.gdp.s.du.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>401584.825321795</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>446706.555377476</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>446424.903972932</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>403043.785411848</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>431842.669543684</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>419315.90099105</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>394027.806547289</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>448561.002070795</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>569687.630994124</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.699</t>
+          <t>699358.211433055</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>782122.540424805</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>842370.164041084</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>1024322.7741933</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.126</t>
+          <t>1126061.50896517</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.122</t>
+          <t>1121941.09699172</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>303851.024336563</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>296596.950262435</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>268428.84810929</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>278759.57547843</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>277575.448418346</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>252897.739542149</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>252063.961202068</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>271895.443151274</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>331410.290230152</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>374610.505804585</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>383172.384781259</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>402331.717845237</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>461585.886507078</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>522119.654423703</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>505717.531891943</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>315462.283561051</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>309647.545049405</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>285163.185972849</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>295387.066372967</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>297417.872573246</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>271153.335805991</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>279225.376590248</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>304722.903808066</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>371122.632415416</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>421115.25367313</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>427529.721241833</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>449263.912134608</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>514131.909320811</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>579209.971225272</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>568145.807787772</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17704.0231443909</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17117.6709391217</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13617.0343120138</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16636.3668298385</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16088.9469474049</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14501.4247358027</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15206.6252702142</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16959.9159787165</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21470.1335647291</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25663.396092615</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27727.8085055009</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30462.7976804498</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39977.9108508523</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50062.6600453904</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51427.9447956712</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>624192.679604979</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>687248.390815925</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>708692.570470619</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>703072.278506279</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>480878.834117722</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>550804.005504075</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>469787.736084133</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>436418.205489388</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>465876.94822259</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>567016.255057347</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>763281.219820082</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.943</t>
+          <t>943053.006129781</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1399094.97454209</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>1705011.41132126</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.746</t>
+          <t>1745960.02150987</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>589100.148333665</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>616076.91758078</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>646603.794368652</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>642771.573438189</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>679246.94230926</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>740509.83462958</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>749645.620053657</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>770507.642667873</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>904554.649316175</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.044</t>
+          <t>1043935.47490109</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>1182201.56629845</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1350475.93419131</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.486</t>
+          <t>1486247.73698082</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1584559.58801337</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.433</t>
+          <t>1432937.67351739</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1159524.49397647</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>1386233.42996616</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1547559.77293067</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1640148.79206782</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>1703645.59265765</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.856</t>
+          <t>1855549.89707523</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.016</t>
+          <t>2015905.27948061</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.157</t>
+          <t>2156678.03085576</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.387</t>
+          <t>2387209.79211688</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2.843</t>
+          <t>2842950.87192523</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3.232</t>
+          <t>3232277.74592173</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3.759</t>
+          <t>3759440.62470553</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4.693</t>
+          <t>4692891.28783348</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6.068</t>
+          <t>6068269.70263788</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6.688</t>
+          <t>6688359.42871218</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8383.27165302559</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8680.40168968542</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8558.39858316071</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9040.54892969407</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9125.7137515814</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8478.1924729092</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8620.50931253793</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9715.06369884756</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12865.4033829614</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15193.6631891568</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16029.7780852351</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17319.498655498</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19883.916082431</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23330.6609799445</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23805.1741724101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47759.9015182692</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73053.4027122089</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69325.3793321759</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74182.1846867123</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71501.7211194082</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68057.8967211869</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75716.7691074869</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95469.9987486471</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117796.827690087</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137898.409063967</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>155195.203504589</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176103.555961768</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>212981.206337972</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>267712.580414454</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>231965.668778668</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.148</t>
+          <t>3148484.28706616</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.058</t>
+          <t>3057556.1094305</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.736</t>
+          <t>2736093.29671419</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2800270.0054195</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.743</t>
+          <t>2742743.03557084</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.505</t>
+          <t>2505302.09589735</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.499</t>
+          <t>2498707.70668959</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.652</t>
+          <t>2651705.52389423</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.183</t>
+          <t>3183219.35689374</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3.552</t>
+          <t>3552278.23613045</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3.533</t>
+          <t>3533188.11817926</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3630129.03446049</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>4.054</t>
+          <t>4053625.70871316</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>4.456</t>
+          <t>4456244.93386247</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4299736.83045073</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>207564.492619665</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>213137.424361972</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>200321.001626964</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>212297.441362205</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>214612.178606821</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>197069.619846512</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>200842.857799856</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>221386.839326574</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>271928.296057228</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>308773.621659132</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>320041.003267815</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>338496.708589376</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>389136.693572784</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>436804.290509776</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>432028.515871853</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>685149.180152181</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>723174.267817848</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>683370.214575895</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>723851.699674817</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>743643.925229116</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>684029.822061039</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>724707.865327396</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>816065.791963335</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1044660.55296486</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.228</t>
+          <t>1228080.20014409</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1320924.67741179</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1429728.55785243</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.684</t>
+          <t>1684337.09193602</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1.867</t>
+          <t>1866643.6361689</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>1722826.37353216</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4795.56881493489</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5761.79924773916</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5975.51427730807</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6566.40986214301</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6352.48667760752</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6186.99194149443</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6618.19709166318</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7812.83005286522</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10426.4017085365</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13002.7393991833</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15040.0694326998</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17880.1771381526</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24523.129141784</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29580.9711466861</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23844.4119474994</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170511.451989104</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171580.089086761</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164726.927221784</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>174082.067960813</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175945.046252206</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>163521.443943394</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>169755.44373943</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>184243.182629104</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>225039.008024376</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>259257.720716662</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>272252.652948598</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>287666.397697278</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>331909.741431214</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>378177.762255925</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>355832.998797654</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.592</t>
+          <t>1592479.72738204</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1607993.80873384</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1472999.82725092</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.516</t>
+          <t>1515572.59761256</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1520425.92235709</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>1394167.43940641</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1422693.96617389</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1574666.47406632</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.942</t>
+          <t>1942162.4269654</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.224</t>
+          <t>2223502.06835081</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.303</t>
+          <t>2302536.24887913</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.408</t>
+          <t>2407689.80863973</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2.749</t>
+          <t>2749198.01023791</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3050111.33827569</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.924</t>
+          <t>2923757.87399039</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.332</t>
+          <t>1331662.62476976</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.382</t>
+          <t>1381969.30685058</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1546717.51716233</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.687</t>
+          <t>1687121.11374715</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.736</t>
+          <t>1736497.22132131</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.737</t>
+          <t>1736506.9175088</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.743</t>
+          <t>1743237.15761697</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.912</t>
+          <t>1912487.03640194</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.197</t>
+          <t>2196997.29974511</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.604</t>
+          <t>2603823.26417647</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2.739</t>
+          <t>2739094.35520131</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2.924</t>
+          <t>2924174.07653427</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>3.348</t>
+          <t>3348212.53002904</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3.177</t>
+          <t>3177127.59304861</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.761</t>
+          <t>2760776.62815445</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108145.108506881</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>115436.715909527</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116248.169236657</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118865.950179077</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>125383.79262426</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>114840.014292548</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>114873.646506726</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>143974.484428496</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>188630.740288044</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>219862.912813148</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>229232.85319412</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>253362.719259374</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>292133.937573393</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>319589.515584532</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>318242.311317524</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54960.603266705</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54003.5583466529</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55061.2700141252</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55942.0706475024</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55490.7260263588</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56709.0671654374</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61874.8058691657</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76967.8464588136</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96576.3897106105</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117142.052283923</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126606.367393054</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>124953.267722249</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>149098.73685307</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>163585.227672021</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132706.557912192</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>246758.697552624</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>296340.564954603</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>308830.477486581</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126556.925373535</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>197354.623760637</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>212168.66193403</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>192064.782431205</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>229399.581630531</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>270458.535253531</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>277864.172861439</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>286575.176925029</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>386905.658694803</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>456549.580118999</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>557889.448015746</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>608116.772467176</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>464751.220122989</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>462225.190128577</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>528178.564942368</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>517150.458182678</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>538216.626538421</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>565535.869615884</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>595670.984467333</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>615476.494244154</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>708946.566709688</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>824144.0978425</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.965</t>
+          <t>964999.467285376</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1.077</t>
+          <t>1076508.02564932</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1.352</t>
+          <t>1351701.33373941</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1461643.56906982</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1556367.84706584</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82082.8023604105</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88615.1183539</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94224.5292737415</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101206.62571322</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>107407.387163901</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>107422.333710186</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118009.585305113</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133181.794345632</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>173134.849044367</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>209802.399484361</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>232625.078990052</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>259600.677781745</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>307004.61053862</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>345034.02830846</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>309482.435573494</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1311273.96831603</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.484</t>
+          <t>1483870.06989474</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.452</t>
+          <t>1451603.58377205</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>1438889.8182629</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1420388.08869068</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.288</t>
+          <t>1288007.54273414</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1323634.354091</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1459319.93794326</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1815074.21168117</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2.066</t>
+          <t>2066101.26890941</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2.143</t>
+          <t>2143474.07062831</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2249900.88946308</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2549678.93860953</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2.826</t>
+          <t>2826071.08681439</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2.648</t>
+          <t>2648398.54716791</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5.872</t>
+          <t>5871890.42551981</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.119</t>
+          <t>5118665.81030177</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4.785</t>
+          <t>4785253.9309269</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4.405</t>
+          <t>4404651.94881297</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5.037</t>
+          <t>5037071.98982695</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5.349</t>
+          <t>5349404.16493955</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4.691</t>
+          <t>4691160.82929384</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4.444</t>
+          <t>4443592.83329258</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4.726</t>
+          <t>4725672.41241039</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5099590.60690422</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>4.963</t>
+          <t>4962887.99128358</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4.696</t>
+          <t>4695724.25121022</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4.712</t>
+          <t>4711722.36995556</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>5.166</t>
+          <t>5165516.10091682</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>5.338</t>
+          <t>5338397.30244155</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.861</t>
+          <t>861460.301026862</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.962</t>
+          <t>962105.707341543</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>905200.759965294</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>593928.099946987</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>711535.595040002</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>820081.544451802</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>814349.103583612</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>920275.675863566</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>1053593.91097591</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.185</t>
+          <t>1185037.67929723</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.418</t>
+          <t>1417806.15148464</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1579464.32138535</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.718</t>
+          <t>1718147.70764043</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1543252.23997828</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.404</t>
+          <t>1404219.06011381</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6870.25180494468</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9288.67320453443</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11861.3793305046</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13380.3325522473</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13272.9463702031</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13114.7122837812</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13951.9927478958</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15539.50324998</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20514.3606892322</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26104.0095630097</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29781.4812486814</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35101.7454686806</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45931.6326006186</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55384.1637183606</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44688.4875258831</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17239.3108033236</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17016.3512237236</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15736.5858882031</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16408.5516894227</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16799.7083117805</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16213.644839205</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17150.2766744441</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19569.6315299784</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25011.4812281777</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29335.515738649</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31294.6043937728</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33142.9560948916</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38304.9369864794</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46078.3507819642</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47587.1543247854</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5588.99670385843</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6328.32546294936</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7381.83142699275</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7497.23374100324</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7581.54931727301</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7590.16027034891</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7882.05190520486</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8616.55921637493</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10557.1109380138</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12666.2966714296</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16151.6882860868</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20773.5520772958</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31224.1884250036</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39034.0517231036</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25431.9017967692</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>221684.806820082</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>246483.466116803</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>313836.8672737</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>353512.487547768</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>416645.48055331</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>513089.70475175</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>581649.151905797</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>604423.719926987</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>578154.596577378</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>596878.101741576</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>661807.614044813</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>713827.587041972</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>761868.585427891</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>800867.03070131</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>652935.983926212</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3561.3187949198</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3801.43526999835</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3776.57486183372</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4085.871506591</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4190.90540539559</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4038.18539125037</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4273.94396265231</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4798.16977936129</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5674.44262185373</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6229.63125339152</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6379.3022237218</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6659.64872455855</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7506.92509221523</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10335.1172703343</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9362.29039042824</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>442432.003995339</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>442009.158975831</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>410605.257385623</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>435488.986505776</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>448600.353435524</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>422872.10990973</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>442074.25322783</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>496800.457689094</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>616390.156955768</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>702195.211113388</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>712538.347873183</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>742314.076188473</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>849674.157739217</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>962664.691582599</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.949</t>
+          <t>948952.413160471</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>328586.634851649</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>361205.151239148</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>369929.407680953</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>428484.969084629</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>431357.1905084</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>326198.993764101</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>324708.742603435</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>310146.821070063</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>319590.12326562</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>353276.001067812</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>418793.50846293</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>440866.291850127</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>532760.961989186</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>691250.951591501</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>557006.145015977</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>127240.024482244</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>137006.514181143</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134892.283263003</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145203.005473805</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149778.237068491</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143270.008275098</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149510.115359812</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166052.915203629</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>201096.207212242</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228868.284447528</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>235627.887793496</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>243111.007411007</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>275537.051519301</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>302897.525931223</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>290985.187087169</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59078.6124607913</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60526.4973218964</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51952.2514207471</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76584.913807596</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56249.8702308697</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65772.8282134102</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>84392.6891708092</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94976.1487282795</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123310.018313421</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>114821.668439314</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>177503.491664955</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>220111.099674611</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>285922.878664554</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>367201.603005224</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>279911.358865086</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>382633.504837727</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>472298.179618165</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>482704.168305107</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>371315.080938553</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222926.404564992</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>291830.176464302</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>341080.234988712</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>413272.199363746</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>499515.104353072</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>657616.754810913</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>834191.171582937</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1059650.53083972</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.377</t>
+          <t>1377332.856956</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.739</t>
+          <t>1738779.81801378</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.291</t>
+          <t>1290674.20826586</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15249.1093362506</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16898.3892949043</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18161.0896123073</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18858.9196340002</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16365.1617196085</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16404.5212929492</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16634.1031094906</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19189.2936179011</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26439.2844668054</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32629.9110878768</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36548.0344549985</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42475.1096600688</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56067.8775486219</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74068.2153629914</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71661.2084640172</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35538.3271567305</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34362.5309734312</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32650.9672537832</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34136.9970773824</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34000.5256505839</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31341.9253539704</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32238.4477431094</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35633.834172735</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43778.4560322476</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51281.4373720044</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54312.9880509822</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57520.8010421065</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68321.4610485979</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80805.3946108564</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75976.4534662208</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>294803.723292731</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>336644.921951737</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>313917.760906402</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>319244.544569752</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>318515.482118483</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>317600.887566823</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>306013.634153545</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>339666.794669754</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>423979.33754236</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>483439.11952559</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>490439.275952524</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.508</t>
+          <t>507886.895964812</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>598667.6121334</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>637875.324693218</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>550558.18538744</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>173213.160081355</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>206577.303529011</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>235019.362135253</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>265839.638960041</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>271845.574436207</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>278326.918335255</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>195515.849158371</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>217689.057139922</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>280361.32846478</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>361401.783050407</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>467395.380555382</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>489817.283367079</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>595421.658264791</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>676344.057806311</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>570099.778129574</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>286809.760049432</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>297795.995147675</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>301998.602914675</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>271348.584481209</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>290714.116729204</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>304353.007310137</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>278116.640335854</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>264451.223015336</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>267392.133133879</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>282890.580370451</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>312751.820271516</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>327367.624360336</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>339724.15139163</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>356792.674443331</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>326704.085773693</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5.926</t>
+          <t>5925561.81252014</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6.217</t>
+          <t>6216538.08802282</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>6710281.87103648</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>7.359</t>
+          <t>7359194.46616187</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>7.887</t>
+          <t>7886668.92980721</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8.524</t>
+          <t>8524048.7152028</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8.811</t>
+          <t>8811213.40462368</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>9.067</t>
+          <t>9066727.56778185</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>9.462</t>
+          <t>9461664.22140888</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>10.014</t>
+          <t>10013628.6690364</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>10.436</t>
+          <t>10436038.7001114</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>11.159</t>
+          <t>11158944.7135162</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>11.673</t>
+          <t>11673229.4662248</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>11.992</t>
+          <t>11991651.2836207</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>11.469</t>
+          <t>11469215.406415</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2.549</t>
+          <t>2549260.64462196</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.786</t>
+          <t>2785657.69799042</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2.835</t>
+          <t>2835265.50343275</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2.669</t>
+          <t>2668528.32312169</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2.769</t>
+          <t>2769408.70234245</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3110234.41560974</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3.058</t>
+          <t>3058202.4638203</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3.114</t>
+          <t>3114340.65030867</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>3.556</t>
+          <t>3556470.70058675</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>4.294</t>
+          <t>4293838.3812946</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>5.177</t>
+          <t>5176545.45398059</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>6.081</t>
+          <t>6080968.29112018</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>6.997</t>
+          <t>6996996.65430016</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>9.152</t>
+          <t>9151796.95523925</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>7889649.97721955</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>30.485</t>
+          <t>30484885.1135298</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>31.234</t>
+          <t>31234235.4846779</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>31.299</t>
+          <t>31299151.2366278</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>31.329</t>
+          <t>31329108.3113332</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>32.655</t>
+          <t>32655313.5256945</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>33.769</t>
+          <t>33768522.6717612</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>33.603</t>
+          <t>33603008.965126</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>35.093</t>
+          <t>35093379.0794744</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>39.548</t>
+          <t>39548414.3301566</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>44.563</t>
+          <t>44563106.4386975</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>47.935</t>
+          <t>47934923.0020402</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>51.814</t>
+          <t>51813544.9978252</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>58.503</t>
+          <t>58502590.7790522</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>65.687</t>
+          <t>65687436.6897506</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>62.306</t>
+          <t>62306395.040176</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gdp.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
